--- a/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-22T16:14:21+00:00</t>
+    <t>2023-03-24T10:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T10:23:48+00:00</t>
+    <t>2023-03-25T12:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mes-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-25T12:16:31+00:00</t>
+    <t>2023-04-02T16:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
